--- a/crm_jaabogados.xlsx
+++ b/crm_jaabogados.xlsx
@@ -842,7 +842,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Medellín, Colombia  |  Actualizado: 24/06/2026</t>
+          <t>Medellín, Colombia  |  Actualizado: 29/06/2026</t>
         </is>
       </c>
     </row>
